--- a/Master/2208r1/2208r1 @ 0.250 IPR_cutlet_data.xlsx
+++ b/Master/2208r1/2208r1 @ 0.250 IPR_cutlet_data.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1734,359 +1734,359 @@
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
-        <v>5.243</v>
+        <v>1.261</v>
       </c>
       <c r="B65" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C65" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>5.6502</v>
+        <v>5.638</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>-0.819</v>
+        <v>-3.0808</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>0.0007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
-        <v>4.144</v>
+        <v>5.264</v>
       </c>
       <c r="B66" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C66" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D66" s="7" t="n">
-        <v>5.682</v>
+        <v>5.6402</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>-0.9778</v>
+        <v>-3.2643</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>0.016</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
-        <v>4.244</v>
+        <v>6.263</v>
       </c>
       <c r="B67" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C67" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>5.7109</v>
+        <v>5.641</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>-0.9562</v>
+        <v>-3.1168</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0003</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
-        <v>3.145</v>
+        <v>4.265</v>
       </c>
       <c r="B68" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C68" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D68" s="7" t="n">
-        <v>5.7273</v>
+        <v>5.6412</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>-1.0969</v>
+        <v>-3.4101</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>0.0104</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
-        <v>3.245</v>
+        <v>5.243</v>
       </c>
       <c r="B69" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C69" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D69" s="7" t="n">
-        <v>5.7673</v>
+        <v>5.6502</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>-1.0977</v>
+        <v>-0.819</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0007</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
-        <v>7.148</v>
+        <v>4.144</v>
       </c>
       <c r="B70" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C70" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D70" s="7" t="n">
-        <v>5.8381</v>
+        <v>5.682</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>-1.262</v>
+        <v>-0.9778</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>0.0245</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
-        <v>6.149</v>
+        <v>4.244</v>
       </c>
       <c r="B71" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C71" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D71" s="7" t="n">
-        <v>5.8852</v>
+        <v>5.7109</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>-1.4071</v>
+        <v>-0.9562</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>0.0219</v>
+        <v>0.0005999999999999999</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n">
-        <v>7.248</v>
+        <v>3.145</v>
       </c>
       <c r="B72" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D72" s="7" t="n">
-        <v>5.9109</v>
+        <v>5.7273</v>
       </c>
       <c r="E72" s="7" t="n">
-        <v>-1.2736</v>
+        <v>-1.0969</v>
       </c>
       <c r="F72" s="7" t="n">
-        <v>0.0005</v>
+        <v>0.0104</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
-        <v>6.249</v>
+        <v>3.245</v>
       </c>
       <c r="B73" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C73" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D73" s="7" t="n">
-        <v>5.95</v>
+        <v>5.7673</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>-1.4183</v>
+        <v>-1.0977</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>0.0004</v>
+        <v>0.0005999999999999999</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
-        <v>5.15</v>
+        <v>7.148</v>
       </c>
       <c r="B74" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C74" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D74" s="7" t="n">
-        <v>5.9574</v>
+        <v>5.8381</v>
       </c>
       <c r="E74" s="7" t="n">
-        <v>-1.5721</v>
+        <v>-1.262</v>
       </c>
       <c r="F74" s="7" t="n">
-        <v>0.012</v>
+        <v>0.0245</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
-        <v>5.25</v>
+        <v>6.149</v>
       </c>
       <c r="B75" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C75" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>5.9848</v>
+        <v>5.8852</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>-1.5616</v>
+        <v>-1.4071</v>
       </c>
       <c r="F75" s="7" t="n">
-        <v>0.0004</v>
+        <v>0.0219</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n">
-        <v>4.251</v>
+        <v>7.248</v>
       </c>
       <c r="B76" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C76" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D76" s="7" t="n">
-        <v>6.0154</v>
+        <v>5.9109</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>-1.712</v>
+        <v>-1.2736</v>
       </c>
       <c r="F76" s="7" t="n">
-        <v>0.0004</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="n">
-        <v>4.151</v>
+        <v>6.249</v>
       </c>
       <c r="B77" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C77" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D77" s="7" t="n">
-        <v>6.0157</v>
+        <v>5.95</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>-1.7633</v>
+        <v>-1.4183</v>
       </c>
       <c r="F77" s="7" t="n">
-        <v>0.0078</v>
+        <v>0.0004</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="n">
-        <v>2.253</v>
+        <v>5.15</v>
       </c>
       <c r="B78" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C78" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D78" s="7" t="n">
-        <v>6.0352</v>
+        <v>5.9574</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>-1.9578</v>
+        <v>-1.5721</v>
       </c>
       <c r="F78" s="7" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="n">
-        <v>3.252</v>
+        <v>5.25</v>
       </c>
       <c r="B79" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C79" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>6.0424</v>
+        <v>5.9848</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>-1.8678</v>
+        <v>-1.5616</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>0.0003</v>
+        <v>0.0004</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n">
-        <v>3.152</v>
+        <v>4.251</v>
       </c>
       <c r="B80" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C80" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D80" s="7" t="n">
-        <v>6.0431</v>
+        <v>6.0154</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>-1.913</v>
+        <v>-1.712</v>
       </c>
       <c r="F80" s="7" t="n">
-        <v>0.0055</v>
+        <v>0.0004</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
-        <v>1.154</v>
+        <v>4.151</v>
       </c>
       <c r="B81" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C81" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>6.0622</v>
+        <v>6.0157</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>-2.122</v>
+        <v>-1.7633</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>0</v>
+        <v>0.0078</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="n">
-        <v>1.254</v>
+        <v>2.253</v>
       </c>
       <c r="B82" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C82" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D82" s="7" t="n">
-        <v>6.0671</v>
+        <v>6.0352</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>-2.1277</v>
+        <v>-1.9578</v>
       </c>
       <c r="F82" s="7" t="n">
         <v>0</v>
@@ -2094,142 +2094,222 @@
     </row>
     <row r="83">
       <c r="A83" s="6" t="n">
-        <v>7.155</v>
+        <v>3.252</v>
       </c>
       <c r="B83" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C83" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D83" s="7" t="n">
-        <v>6.0832</v>
+        <v>6.0424</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>-2.0917</v>
+        <v>-1.8678</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>0.0094</v>
+        <v>0.0003</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n">
-        <v>6.156</v>
+        <v>3.152</v>
       </c>
       <c r="B84" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C84" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D84" s="7" t="n">
-        <v>6.0973</v>
+        <v>6.0431</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>-2.2427</v>
+        <v>-1.913</v>
       </c>
       <c r="F84" s="7" t="n">
-        <v>0.0066</v>
+        <v>0.0055</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="n">
-        <v>7.255</v>
+        <v>1.154</v>
       </c>
       <c r="B85" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C85" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>6.0992</v>
+        <v>6.0622</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>-2.0641</v>
+        <v>-2.122</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="n">
-        <v>6.256</v>
+        <v>1.254</v>
       </c>
       <c r="B86" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C86" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D86" s="7" t="n">
-        <v>6.1083</v>
+        <v>6.0671</v>
       </c>
       <c r="E86" s="7" t="n">
-        <v>-2.2092</v>
+        <v>-2.1277</v>
       </c>
       <c r="F86" s="7" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="n">
-        <v>5.257</v>
+        <v>7.155</v>
       </c>
       <c r="B87" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C87" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D87" s="7" t="n">
-        <v>6.1198</v>
+        <v>6.0832</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>-2.37</v>
+        <v>-2.0917</v>
       </c>
       <c r="F87" s="7" t="n">
-        <v>0.0001</v>
+        <v>0.0094</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="n">
+        <v>6.156</v>
+      </c>
+      <c r="B88" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C88" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" s="7" t="n">
+        <v>6.0973</v>
+      </c>
+      <c r="E88" s="7" t="n">
+        <v>-2.2427</v>
+      </c>
+      <c r="F88" s="7" t="n">
+        <v>0.0066</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="n">
+        <v>7.255</v>
+      </c>
+      <c r="B89" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C89" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D89" s="7" t="n">
+        <v>6.0992</v>
+      </c>
+      <c r="E89" s="7" t="n">
+        <v>-2.0641</v>
+      </c>
+      <c r="F89" s="7" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="n">
+        <v>6.256</v>
+      </c>
+      <c r="B90" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C90" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D90" s="7" t="n">
+        <v>6.1083</v>
+      </c>
+      <c r="E90" s="7" t="n">
+        <v>-2.2092</v>
+      </c>
+      <c r="F90" s="7" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="n">
+        <v>5.257</v>
+      </c>
+      <c r="B91" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C91" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D91" s="7" t="n">
+        <v>6.1198</v>
+      </c>
+      <c r="E91" s="7" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="F91" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="n">
         <v>5.157</v>
       </c>
-      <c r="B88" s="6" t="n">
+      <c r="B92" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="C88" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D88" s="7" t="n">
+      <c r="C92" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" s="7" t="n">
         <v>6.1231</v>
       </c>
-      <c r="E88" s="7" t="n">
+      <c r="E92" s="7" t="n">
         <v>-2.434</v>
       </c>
-      <c r="F88" s="7" t="n">
+      <c r="F92" s="7" t="n">
         <v>0.0003</v>
       </c>
     </row>
-    <row r="90">
-      <c r="E90" s="8" t="inlineStr">
+    <row r="94">
+      <c r="E94" s="8" t="inlineStr">
         <is>
           <t>Count:</t>
         </is>
       </c>
-      <c r="F90" s="9" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="E91" s="8" t="inlineStr">
+      <c r="F94" s="9" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="E95" s="8" t="inlineStr">
         <is>
           <t>Total Area:</t>
         </is>
       </c>
-      <c r="F91" s="10" t="n">
-        <v>1.5214</v>
+      <c r="F95" s="10" t="n">
+        <v>1.522</v>
       </c>
     </row>
   </sheetData>
